--- a/artfynd/A 39282-2025 artfynd.xlsx
+++ b/artfynd/A 39282-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY41"/>
+  <dimension ref="A1:AY43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4874,6 +4874,237 @@
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>128970369</v>
+      </c>
+      <c r="B42" t="n">
+        <v>57720</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Strömborgen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>459223</v>
+      </c>
+      <c r="R42" t="n">
+        <v>6987032</v>
+      </c>
+      <c r="S42" t="n">
+        <v>10</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Oviken</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Sågs födosökande lågt ner på stammen av granar.</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>128970371</v>
+      </c>
+      <c r="B43" t="n">
+        <v>57824</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>103031</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Lavskrika</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Perisoreus infaustus</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Strömborgen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>459308</v>
+      </c>
+      <c r="R43" t="n">
+        <v>6987027</v>
+      </c>
+      <c r="S43" t="n">
+        <v>10</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Oviken</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 39282-2025 artfynd.xlsx
+++ b/artfynd/A 39282-2025 artfynd.xlsx
@@ -4879,7 +4879,7 @@
         <v>128970369</v>
       </c>
       <c r="B42" t="n">
-        <v>57720</v>
+        <v>57723</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4997,7 +4997,7 @@
         <v>128970371</v>
       </c>
       <c r="B43" t="n">
-        <v>57824</v>
+        <v>57827</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>

--- a/artfynd/A 39282-2025 artfynd.xlsx
+++ b/artfynd/A 39282-2025 artfynd.xlsx
@@ -4879,7 +4879,7 @@
         <v>128970369</v>
       </c>
       <c r="B42" t="n">
-        <v>57723</v>
+        <v>57725</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4997,7 +4997,7 @@
         <v>128970371</v>
       </c>
       <c r="B43" t="n">
-        <v>57827</v>
+        <v>57829</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>

--- a/artfynd/A 39282-2025 artfynd.xlsx
+++ b/artfynd/A 39282-2025 artfynd.xlsx
@@ -4879,7 +4879,7 @@
         <v>128970369</v>
       </c>
       <c r="B42" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4997,7 +4997,7 @@
         <v>128970371</v>
       </c>
       <c r="B43" t="n">
-        <v>57829</v>
+        <v>57831</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>

--- a/artfynd/A 39282-2025 artfynd.xlsx
+++ b/artfynd/A 39282-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY43"/>
+  <dimension ref="A1:AY45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5105,6 +5105,210 @@
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>129593946</v>
+      </c>
+      <c r="B44" t="n">
+        <v>57727</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Strömborgen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>459006</v>
+      </c>
+      <c r="R44" t="n">
+        <v>6987174</v>
+      </c>
+      <c r="S44" t="n">
+        <v>10</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Oviken</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2025-11-07</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2025-11-07</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>129593950</v>
+      </c>
+      <c r="B45" t="n">
+        <v>57727</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Strömborgen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>459005</v>
+      </c>
+      <c r="R45" t="n">
+        <v>6987136</v>
+      </c>
+      <c r="S45" t="n">
+        <v>10</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Oviken</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2025-11-07</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2025-11-07</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 39282-2025 artfynd.xlsx
+++ b/artfynd/A 39282-2025 artfynd.xlsx
@@ -5110,7 +5110,7 @@
         <v>129593946</v>
       </c>
       <c r="B44" t="n">
-        <v>57727</v>
+        <v>57730</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5212,7 +5212,7 @@
         <v>129593950</v>
       </c>
       <c r="B45" t="n">
-        <v>57727</v>
+        <v>57730</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>

--- a/artfynd/A 39282-2025 artfynd.xlsx
+++ b/artfynd/A 39282-2025 artfynd.xlsx
@@ -4879,7 +4879,7 @@
         <v>128970369</v>
       </c>
       <c r="B42" t="n">
-        <v>57727</v>
+        <v>57735</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5110,7 +5110,7 @@
         <v>129593946</v>
       </c>
       <c r="B44" t="n">
-        <v>57730</v>
+        <v>57735</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5212,7 +5212,7 @@
         <v>129593950</v>
       </c>
       <c r="B45" t="n">
-        <v>57730</v>
+        <v>57735</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>

--- a/artfynd/A 39282-2025 artfynd.xlsx
+++ b/artfynd/A 39282-2025 artfynd.xlsx
@@ -4879,7 +4879,7 @@
         <v>128970369</v>
       </c>
       <c r="B42" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5110,7 +5110,7 @@
         <v>129593946</v>
       </c>
       <c r="B44" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5212,7 +5212,7 @@
         <v>129593950</v>
       </c>
       <c r="B45" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>

--- a/artfynd/A 39282-2025 artfynd.xlsx
+++ b/artfynd/A 39282-2025 artfynd.xlsx
@@ -4879,7 +4879,7 @@
         <v>128970369</v>
       </c>
       <c r="B42" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5110,7 +5110,7 @@
         <v>129593946</v>
       </c>
       <c r="B44" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5212,7 +5212,7 @@
         <v>129593950</v>
       </c>
       <c r="B45" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>

--- a/artfynd/A 39282-2025 artfynd.xlsx
+++ b/artfynd/A 39282-2025 artfynd.xlsx
@@ -4879,7 +4879,7 @@
         <v>128970369</v>
       </c>
       <c r="B42" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5110,7 +5110,7 @@
         <v>129593946</v>
       </c>
       <c r="B44" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5212,7 +5212,7 @@
         <v>129593950</v>
       </c>
       <c r="B45" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>

--- a/artfynd/A 39282-2025 artfynd.xlsx
+++ b/artfynd/A 39282-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY45"/>
+  <dimension ref="A1:AY65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120972401</v>
+        <v>121210350</v>
       </c>
       <c r="B2" t="n">
-        <v>90727</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,34 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Stenmyrflon, Stenmyrflon, Jmt</t>
+          <t>Strömborgsmyren, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>459577</v>
+        <v>459166</v>
       </c>
       <c r="R2" t="n">
-        <v>6986952</v>
+        <v>6987016</v>
       </c>
       <c r="S2" t="n">
         <v>20</v>
@@ -745,22 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>14:05</t>
+          <t>2024-11-16</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>14:05</t>
+          <t>2024-11-16</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -775,27 +760,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Jenny Persson</t>
+          <t>Klas Andersson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Jenny Persson</t>
+          <t>Klas Andersson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120971712</v>
+        <v>121210351</v>
       </c>
       <c r="B3" t="n">
-        <v>90709</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -823,14 +803,14 @@
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Strömborgsmyren, Strömborgsmyren, Jmt</t>
+          <t>Strömborgsmyren, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>459526</v>
+        <v>459109</v>
       </c>
       <c r="R3" t="n">
-        <v>6987171</v>
+        <v>6987053</v>
       </c>
       <c r="S3" t="n">
         <v>20</v>
@@ -857,22 +837,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>13:36</t>
+          <t>2024-11-16</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>13:36</t>
+          <t>2024-11-16</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -887,27 +857,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Jenny Persson</t>
+          <t>Klas Andersson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Jenny Persson</t>
+          <t>Klas Andersson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120972337</v>
+        <v>121210321</v>
       </c>
       <c r="B4" t="n">
-        <v>78604</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -915,34 +880,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Stenmyrflon, Stenmyrflon, Jmt</t>
+          <t>Strömborgsmyren, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>459550</v>
+        <v>459138</v>
       </c>
       <c r="R4" t="n">
-        <v>6986963</v>
+        <v>6987016</v>
       </c>
       <c r="S4" t="n">
         <v>20</v>
@@ -969,22 +934,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>14:02</t>
+          <t>2024-11-16</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>14:02</t>
+          <t>2024-11-16</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -999,31 +954,26 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Jenny Persson</t>
+          <t>Klas Andersson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Jenny Persson</t>
+          <t>Klas Andersson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120972218</v>
+        <v>121210356</v>
       </c>
       <c r="B5" t="n">
-        <v>78604</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -1047,14 +997,14 @@
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Stenmyrflon, Stenmyrflon, Jmt</t>
+          <t>Strömborgsmyren, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>459512</v>
+        <v>459060</v>
       </c>
       <c r="R5" t="n">
-        <v>6987017</v>
+        <v>6987110</v>
       </c>
       <c r="S5" t="n">
         <v>20</v>
@@ -1081,22 +1031,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>13:56</t>
+          <t>2024-11-16</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>13:56</t>
+          <t>2024-11-16</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1111,31 +1051,26 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Jenny Persson</t>
+          <t>Klas Andersson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Jenny Persson</t>
+          <t>Klas Andersson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120971669</v>
+        <v>121210358</v>
       </c>
       <c r="B6" t="n">
-        <v>78604</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -1159,14 +1094,14 @@
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Strömborgsmyren, Strömborgsmyren, Jmt</t>
+          <t>Strömborgsmyren, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>459573</v>
+        <v>459058</v>
       </c>
       <c r="R6" t="n">
-        <v>6987191</v>
+        <v>6987172</v>
       </c>
       <c r="S6" t="n">
         <v>20</v>
@@ -1193,22 +1128,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>13:32</t>
+          <t>2024-11-16</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>13:32</t>
+          <t>2024-11-16</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1223,65 +1148,60 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Jenny Persson</t>
+          <t>Klas Andersson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Jenny Persson</t>
+          <t>Klas Andersson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121125668</v>
+        <v>121227120</v>
       </c>
       <c r="B7" t="n">
-        <v>90713</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Stenmyrflon, Stenmyrflon, Jmt</t>
+          <t>Strömborgsmyren, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>459429</v>
+        <v>459057</v>
       </c>
       <c r="R7" t="n">
-        <v>6986951</v>
+        <v>6987082</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1305,22 +1225,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2024-11-11</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>09:55</t>
+          <t>2024-11-17</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2024-11-11</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>09:55</t>
+          <t>2024-11-17</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1335,69 +1245,60 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Jenny Persson</t>
+          <t>Klas Andersson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Jenny Persson</t>
+          <t>Klas Andersson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121210315</v>
+        <v>121227121</v>
       </c>
       <c r="B8" t="n">
-        <v>57356</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Strömborgsmyren, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>459269</v>
+        <v>459050</v>
       </c>
       <c r="R8" t="n">
-        <v>6987021</v>
+        <v>6987112</v>
       </c>
       <c r="S8" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1421,17 +1322,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2024-11-16</t>
+          <t>2024-11-17</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2024-11-16</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Rel. färska ringhack på gran, hördes också varnande</t>
+          <t>2024-11-17</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1458,37 +1354,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121210350</v>
+        <v>121227122</v>
       </c>
       <c r="B9" t="n">
-        <v>90720</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1498,13 +1389,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>459166</v>
+        <v>459010</v>
       </c>
       <c r="R9" t="n">
-        <v>6987016</v>
+        <v>6987146</v>
       </c>
       <c r="S9" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1528,12 +1419,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2024-11-16</t>
+          <t>2024-11-17</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2024-11-16</t>
+          <t>2024-11-17</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1560,15 +1451,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121210330</v>
+        <v>121227123</v>
       </c>
       <c r="B10" t="n">
-        <v>74706</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1576,40 +1462,37 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>492</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Smalskaftslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Chaenotheca gracilenta</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Strömborgsmyren, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>459263</v>
+        <v>458981</v>
       </c>
       <c r="R10" t="n">
-        <v>6987015</v>
+        <v>6987164</v>
       </c>
       <c r="S10" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1633,17 +1516,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2024-11-16</t>
+          <t>2024-11-17</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2024-11-16</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Rikligt i granstubbe, se bild.</t>
+          <t>2024-11-17</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1652,7 +1530,6 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1671,15 +1548,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121210319</v>
+        <v>121227095</v>
       </c>
       <c r="B11" t="n">
-        <v>57509</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83307</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1687,21 +1559,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>103021</v>
+        <v>6440</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1711,13 +1583,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>459169</v>
+        <v>459081</v>
       </c>
       <c r="R11" t="n">
-        <v>6987016</v>
+        <v>6987161</v>
       </c>
       <c r="S11" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1741,12 +1613,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2024-11-16</t>
+          <t>2024-11-17</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2024-11-16</t>
+          <t>2024-11-17</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1773,15 +1645,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121210351</v>
+        <v>121227096</v>
       </c>
       <c r="B12" t="n">
-        <v>90720</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83307</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1789,21 +1656,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1202</v>
+        <v>6440</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1813,13 +1680,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>459109</v>
+        <v>459090</v>
       </c>
       <c r="R12" t="n">
-        <v>6987053</v>
+        <v>6987125</v>
       </c>
       <c r="S12" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1843,12 +1710,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2024-11-16</t>
+          <t>2024-11-17</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2024-11-16</t>
+          <t>2024-11-17</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1875,15 +1742,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121210334</v>
+        <v>121227097</v>
       </c>
       <c r="B13" t="n">
-        <v>74715</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83307</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1915,13 +1777,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>459371</v>
+        <v>459089</v>
       </c>
       <c r="R13" t="n">
-        <v>6987042</v>
+        <v>6987126</v>
       </c>
       <c r="S13" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1945,12 +1807,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2024-11-16</t>
+          <t>2024-11-17</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2024-11-16</t>
+          <t>2024-11-17</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1977,15 +1839,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121210321</v>
+        <v>121227094</v>
       </c>
       <c r="B14" t="n">
-        <v>82393</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1993,21 +1850,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1312</v>
+        <v>6458</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2017,13 +1874,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>459138</v>
+        <v>458978</v>
       </c>
       <c r="R14" t="n">
-        <v>6987016</v>
+        <v>6987169</v>
       </c>
       <c r="S14" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2047,12 +1904,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2024-11-16</t>
+          <t>2024-11-17</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2024-11-16</t>
+          <t>2024-11-17</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2079,15 +1936,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121210356</v>
+        <v>121227134</v>
       </c>
       <c r="B15" t="n">
-        <v>78609</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2095,37 +1947,53 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Strömborgsmyren, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>459060</v>
+        <v>458986</v>
       </c>
       <c r="R15" t="n">
-        <v>6987110</v>
+        <v>6987138</v>
       </c>
       <c r="S15" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2149,12 +2017,17 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2024-11-16</t>
+          <t>2024-11-17</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2024-11-16</t>
+          <t>2024-11-17</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Adult födosökande i mosaikartad granskog=&gt;huvudbiotop</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2181,53 +2054,48 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121210331</v>
+        <v>129593946</v>
       </c>
       <c r="B16" t="n">
-        <v>74706</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>492</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Smalskaftslav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Chaenotheca gracilenta</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Strömborgsmyren, Jmt</t>
+          <t>Strömborgen, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>459255</v>
+        <v>459006</v>
       </c>
       <c r="R16" t="n">
-        <v>6987011</v>
+        <v>6987174</v>
       </c>
       <c r="S16" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2251,12 +2119,17 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2024-11-16</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2024-11-16</t>
+          <t>2025-11-07</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2271,27 +2144,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Klas Andersson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Klas Andersson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121227097</v>
+        <v>129593950</v>
       </c>
       <c r="B17" t="n">
-        <v>74715</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2299,37 +2167,37 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Strömborgsmyren, Jmt</t>
+          <t>Strömborgen, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>459089</v>
+        <v>459005</v>
       </c>
       <c r="R17" t="n">
-        <v>6987126</v>
+        <v>6987136</v>
       </c>
       <c r="S17" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2353,12 +2221,17 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2025-11-07</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2373,27 +2246,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Klas Andersson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Klas Andersson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121227109</v>
+        <v>121210319</v>
       </c>
       <c r="B18" t="n">
-        <v>82393</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58114</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2401,21 +2269,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1312</v>
+        <v>103021</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2425,13 +2293,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>459277</v>
+        <v>459169</v>
       </c>
       <c r="R18" t="n">
-        <v>6987050</v>
+        <v>6987016</v>
       </c>
       <c r="S18" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2455,12 +2323,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2024-11-16</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2024-11-16</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2487,15 +2355,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121227123</v>
+        <v>121210313</v>
       </c>
       <c r="B19" t="n">
-        <v>78609</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97358</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2503,21 +2366,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>53</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2527,13 +2390,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>458981</v>
+        <v>459274</v>
       </c>
       <c r="R19" t="n">
-        <v>6987164</v>
+        <v>6987056</v>
       </c>
       <c r="S19" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2557,12 +2420,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2024-11-16</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2024-11-16</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2589,53 +2452,51 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121227101</v>
+        <v>121210330</v>
       </c>
       <c r="B20" t="n">
-        <v>90720</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83298</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1202</v>
+        <v>492</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Smalskaftslav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Chaenotheca gracilenta</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Strömborgsmyren, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>459430</v>
+        <v>459263</v>
       </c>
       <c r="R20" t="n">
-        <v>6986932</v>
+        <v>6987015</v>
       </c>
       <c r="S20" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2659,12 +2520,17 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2024-11-16</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2024-11-16</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Rikligt i granstubbe, se bild.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2673,6 +2539,7 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2691,37 +2558,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121227089</v>
+        <v>121210331</v>
       </c>
       <c r="B21" t="n">
-        <v>91006</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83298</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>658</v>
+        <v>492</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Smalskaftslav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Chaenotheca gracilenta</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2731,13 +2593,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>459514</v>
+        <v>459255</v>
       </c>
       <c r="R21" t="n">
-        <v>6987120</v>
+        <v>6987011</v>
       </c>
       <c r="S21" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2761,12 +2623,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2024-11-16</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2024-11-16</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2793,15 +2655,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121227113</v>
+        <v>121227110</v>
       </c>
       <c r="B22" t="n">
-        <v>74706</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83298</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2827,19 +2684,16 @@
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
-      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Strömborgsmyren, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>459280</v>
+        <v>459494</v>
       </c>
       <c r="R22" t="n">
-        <v>6987044</v>
+        <v>6987097</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -2874,18 +2728,12 @@
           <t>2024-11-17</t>
         </is>
       </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>I liten rothålighet under levande gran, fåtal jmf med de i stubbar</t>
-        </is>
-      </c>
       <c r="AD22" t="b">
         <v>0</v>
       </c>
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -2904,37 +2752,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121227100</v>
+        <v>121227111</v>
       </c>
       <c r="B23" t="n">
-        <v>90738</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83298</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>5432</v>
+        <v>492</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Smalskaftslav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Chaenotheca gracilenta</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2944,10 +2787,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>459252</v>
+        <v>459244</v>
       </c>
       <c r="R23" t="n">
-        <v>6987048</v>
+        <v>6987057</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -3006,50 +2849,48 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121227088</v>
+        <v>121227113</v>
       </c>
       <c r="B24" t="n">
-        <v>74699</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83298</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6439</v>
+        <v>492</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Smalskaftslav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Chaenotheca gracilenta</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Strömborgsmyren, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>459493</v>
+        <v>459280</v>
       </c>
       <c r="R24" t="n">
-        <v>6987097</v>
+        <v>6987044</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3084,12 +2925,18 @@
           <t>2024-11-17</t>
         </is>
       </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>I liten rothålighet under levande gran, fåtal jmf med de i stubbar</t>
+        </is>
+      </c>
       <c r="AD24" t="b">
         <v>0</v>
       </c>
       <c r="AE24" t="b">
         <v>0</v>
       </c>
+      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -3108,15 +2955,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121227105</v>
+        <v>121210318</v>
       </c>
       <c r="B25" t="n">
-        <v>82393</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3124,21 +2966,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1312</v>
+        <v>658</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3148,13 +2990,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>459387</v>
+        <v>459210</v>
       </c>
       <c r="R25" t="n">
-        <v>6987097</v>
+        <v>6986977</v>
       </c>
       <c r="S25" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3178,12 +3020,12 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2024-11-16</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2024-11-16</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3210,37 +3052,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121227110</v>
+        <v>121227089</v>
       </c>
       <c r="B26" t="n">
-        <v>74706</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>492</v>
+        <v>658</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Smalskaftslav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Chaenotheca gracilenta</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3250,10 +3087,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>459494</v>
+        <v>459514</v>
       </c>
       <c r="R26" t="n">
-        <v>6987097</v>
+        <v>6987120</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3312,15 +3149,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121227118</v>
+        <v>121210316</v>
       </c>
       <c r="B27" t="n">
-        <v>78609</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91905</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3328,21 +3160,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3352,13 +3184,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>459411</v>
+        <v>459238</v>
       </c>
       <c r="R27" t="n">
-        <v>6987131</v>
+        <v>6986977</v>
       </c>
       <c r="S27" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3382,12 +3214,12 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2024-11-16</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2024-11-16</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3414,15 +3246,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121227094</v>
+        <v>120971712</v>
       </c>
       <c r="B28" t="n">
-        <v>79690</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3430,37 +3257,37 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Strömborgsmyren, Jmt</t>
+          <t>Strömborgsmyren, Strömborgsmyren, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>458978</v>
+        <v>459526</v>
       </c>
       <c r="R28" t="n">
-        <v>6987169</v>
+        <v>6987171</v>
       </c>
       <c r="S28" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3484,12 +3311,22 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2024-11-06</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2024-11-06</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3504,27 +3341,22 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Klas Andersson</t>
+          <t>Jenny Persson</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Klas Andersson</t>
+          <t>Jenny Persson</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121227096</v>
+        <v>121125668</v>
       </c>
       <c r="B29" t="n">
-        <v>74715</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3532,37 +3364,37 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6440</v>
+        <v>1202</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Strömborgsmyren, Jmt</t>
+          <t>Stenmyrflon, Stenmyrflon, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>459090</v>
+        <v>459429</v>
       </c>
       <c r="R29" t="n">
-        <v>6987125</v>
+        <v>6986951</v>
       </c>
       <c r="S29" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3586,12 +3418,22 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2024-11-11</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>09:55</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2024-11-11</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>09:55</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3606,27 +3448,22 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Klas Andersson</t>
+          <t>Jenny Persson</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Klas Andersson</t>
+          <t>Jenny Persson</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121227120</v>
+        <v>121227101</v>
       </c>
       <c r="B30" t="n">
-        <v>78609</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3634,21 +3471,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3658,10 +3495,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>459057</v>
+        <v>459430</v>
       </c>
       <c r="R30" t="n">
-        <v>6987082</v>
+        <v>6986932</v>
       </c>
       <c r="S30" t="n">
         <v>25</v>
@@ -3720,15 +3557,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>121227121</v>
+        <v>121227102</v>
       </c>
       <c r="B31" t="n">
-        <v>78609</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3736,21 +3568,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3760,10 +3592,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>459050</v>
+        <v>459461</v>
       </c>
       <c r="R31" t="n">
-        <v>6987112</v>
+        <v>6987117</v>
       </c>
       <c r="S31" t="n">
         <v>25</v>
@@ -3822,15 +3654,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>121227102</v>
+        <v>121227103</v>
       </c>
       <c r="B32" t="n">
-        <v>90720</v>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3862,10 +3689,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>459461</v>
+        <v>459515</v>
       </c>
       <c r="R32" t="n">
-        <v>6987117</v>
+        <v>6987120</v>
       </c>
       <c r="S32" t="n">
         <v>25</v>
@@ -3924,15 +3751,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>121227135</v>
+        <v>121227105</v>
       </c>
       <c r="B33" t="n">
-        <v>57356</v>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3940,42 +3762,34 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Strömborgsmyren, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>459252</v>
+        <v>459387</v>
       </c>
       <c r="R33" t="n">
-        <v>6987032</v>
+        <v>6987097</v>
       </c>
       <c r="S33" t="n">
         <v>25</v>
@@ -4008,11 +3822,6 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2024-11-17</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4039,15 +3848,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>121227124</v>
+        <v>121227106</v>
       </c>
       <c r="B34" t="n">
-        <v>78609</v>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4055,21 +3859,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4079,10 +3883,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>459222</v>
+        <v>459365</v>
       </c>
       <c r="R34" t="n">
-        <v>6987047</v>
+        <v>6987091</v>
       </c>
       <c r="S34" t="n">
         <v>25</v>
@@ -4141,15 +3945,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>121227116</v>
+        <v>121227109</v>
       </c>
       <c r="B35" t="n">
-        <v>78609</v>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4157,21 +3956,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4181,10 +3980,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>459437</v>
+        <v>459277</v>
       </c>
       <c r="R35" t="n">
-        <v>6987156</v>
+        <v>6987050</v>
       </c>
       <c r="S35" t="n">
         <v>25</v>
@@ -4243,15 +4042,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>121227134</v>
+        <v>121227086</v>
       </c>
       <c r="B36" t="n">
-        <v>57356</v>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4259,50 +4053,34 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K36" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N36" t="inlineStr"/>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Strömborgsmyren, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>458986</v>
+        <v>459312</v>
       </c>
       <c r="R36" t="n">
-        <v>6987138</v>
+        <v>6986982</v>
       </c>
       <c r="S36" t="n">
         <v>25</v>
@@ -4335,11 +4113,6 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2024-11-17</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Adult födosökande i mosaikartad granskog=&gt;huvudbiotop</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4366,19 +4139,14 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>121227122</v>
+        <v>120971669</v>
       </c>
       <c r="B37" t="n">
-        <v>78609</v>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
@@ -4402,17 +4170,17 @@
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Strömborgsmyren, Jmt</t>
+          <t>Strömborgsmyren, Strömborgsmyren, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>459010</v>
+        <v>459573</v>
       </c>
       <c r="R37" t="n">
-        <v>6987146</v>
+        <v>6987191</v>
       </c>
       <c r="S37" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4436,12 +4204,22 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2024-11-06</t>
+        </is>
+      </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2024-11-06</t>
+        </is>
+      </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4456,65 +4234,60 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Klas Andersson</t>
+          <t>Jenny Persson</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Klas Andersson</t>
+          <t>Jenny Persson</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>121227098</v>
+        <v>120972218</v>
       </c>
       <c r="B38" t="n">
-        <v>90738</v>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Strömborgsmyren, Jmt</t>
+          <t>Stenmyrflon, Stenmyrflon, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>459468</v>
+        <v>459512</v>
       </c>
       <c r="R38" t="n">
-        <v>6987119</v>
+        <v>6987017</v>
       </c>
       <c r="S38" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4538,12 +4311,22 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2024-11-06</t>
+        </is>
+      </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2024-11-06</t>
+        </is>
+      </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4558,65 +4341,60 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Klas Andersson</t>
+          <t>Jenny Persson</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Klas Andersson</t>
+          <t>Jenny Persson</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>121227099</v>
+        <v>120972337</v>
       </c>
       <c r="B39" t="n">
-        <v>90738</v>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Strömborgsmyren, Jmt</t>
+          <t>Stenmyrflon, Stenmyrflon, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>459187</v>
+        <v>459550</v>
       </c>
       <c r="R39" t="n">
-        <v>6987057</v>
+        <v>6986963</v>
       </c>
       <c r="S39" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4640,12 +4418,22 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2024-11-06</t>
+        </is>
+      </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2024-11-06</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4660,65 +4448,60 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Klas Andersson</t>
+          <t>Jenny Persson</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Klas Andersson</t>
+          <t>Jenny Persson</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>121227103</v>
+        <v>121125770</v>
       </c>
       <c r="B40" t="n">
-        <v>90720</v>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Strömborgsmyren, Jmt</t>
+          <t>Stenmyrflon, Stenmyrflon, Jmt</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>459515</v>
+        <v>459416</v>
       </c>
       <c r="R40" t="n">
-        <v>6987120</v>
+        <v>6986950</v>
       </c>
       <c r="S40" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4742,12 +4525,22 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2024-11-11</t>
+        </is>
+      </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2024-11-11</t>
+        </is>
+      </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4762,31 +4555,26 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Klas Andersson</t>
+          <t>Jenny Persson</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Klas Andersson</t>
+          <t>Jenny Persson</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>121227117</v>
+        <v>121125947</v>
       </c>
       <c r="B41" t="n">
-        <v>78609</v>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
@@ -4810,17 +4598,17 @@
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Strömborgsmyren, Jmt</t>
+          <t>Stenmyrflon, Stenmyrflon, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>459430</v>
+        <v>459414</v>
       </c>
       <c r="R41" t="n">
-        <v>6987144</v>
+        <v>6986942</v>
       </c>
       <c r="S41" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -4844,12 +4632,22 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2024-11-11</t>
+        </is>
+      </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2024-11-11</t>
+        </is>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4864,76 +4662,60 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Klas Andersson</t>
+          <t>Jenny Persson</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Klas Andersson</t>
+          <t>Jenny Persson</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128970369</v>
+        <v>121210354</v>
       </c>
       <c r="B42" t="n">
-        <v>57740</v>
+        <v>79327</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K42" t="inlineStr"/>
-      <c r="L42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N42" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Strömborgen, Jmt</t>
+          <t>Strömborgsmyren, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>459223</v>
+        <v>459368</v>
       </c>
       <c r="R42" t="n">
-        <v>6987032</v>
+        <v>6986963</v>
       </c>
       <c r="S42" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -4957,17 +4739,12 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2024-11-16</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>Sågs födosökande lågt ner på stammen av granar.</t>
+          <t>2024-11-16</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4982,76 +4759,60 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Klas Andersson</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Klas Andersson</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128970371</v>
+        <v>121210355</v>
       </c>
       <c r="B43" t="n">
-        <v>57831</v>
+        <v>79327</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>103031</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K43" t="inlineStr"/>
-      <c r="L43" t="inlineStr"/>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N43" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Strömborgen, Jmt</t>
+          <t>Strömborgsmyren, Jmt</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>459308</v>
+        <v>459361</v>
       </c>
       <c r="R43" t="n">
-        <v>6987027</v>
+        <v>6986994</v>
       </c>
       <c r="S43" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5075,12 +4836,12 @@
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2024-11-16</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2024-11-16</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5095,60 +4856,60 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Klas Andersson</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Klas Andersson</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129593946</v>
+        <v>121227114</v>
       </c>
       <c r="B44" t="n">
-        <v>57740</v>
+        <v>79327</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Strömborgen, Jmt</t>
+          <t>Strömborgsmyren, Jmt</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>459006</v>
+        <v>459383</v>
       </c>
       <c r="R44" t="n">
-        <v>6987174</v>
+        <v>6986968</v>
       </c>
       <c r="S44" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5172,17 +4933,12 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2024-11-17</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>2024-11-17</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5197,60 +4953,60 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Klas Andersson</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Klas Andersson</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129593950</v>
+        <v>121227115</v>
       </c>
       <c r="B45" t="n">
-        <v>57740</v>
+        <v>79327</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Strömborgen, Jmt</t>
+          <t>Strömborgsmyren, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>459005</v>
+        <v>459332</v>
       </c>
       <c r="R45" t="n">
-        <v>6987136</v>
+        <v>6986979</v>
       </c>
       <c r="S45" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5274,17 +5030,12 @@
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2024-11-17</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
+          <t>2024-11-17</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5299,15 +5050,2090 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
+          <t>Klas Andersson</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Klas Andersson</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>121227116</v>
+      </c>
+      <c r="B46" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Strömborgsmyren, Jmt</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>459437</v>
+      </c>
+      <c r="R46" t="n">
+        <v>6987156</v>
+      </c>
+      <c r="S46" t="n">
+        <v>25</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Oviken</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2024-11-17</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2024-11-17</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Klas Andersson</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>Klas Andersson</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>121227117</v>
+      </c>
+      <c r="B47" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Strömborgsmyren, Jmt</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>459430</v>
+      </c>
+      <c r="R47" t="n">
+        <v>6987144</v>
+      </c>
+      <c r="S47" t="n">
+        <v>25</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Oviken</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2024-11-17</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2024-11-17</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>Klas Andersson</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>Klas Andersson</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>121227118</v>
+      </c>
+      <c r="B48" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>Strömborgsmyren, Jmt</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>459411</v>
+      </c>
+      <c r="R48" t="n">
+        <v>6987131</v>
+      </c>
+      <c r="S48" t="n">
+        <v>25</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Oviken</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>2024-11-17</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>2024-11-17</t>
+        </is>
+      </c>
+      <c r="AD48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>Klas Andersson</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>Klas Andersson</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>121227119</v>
+      </c>
+      <c r="B49" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>Strömborgsmyren, Jmt</t>
+        </is>
+      </c>
+      <c r="Q49" t="n">
+        <v>459217</v>
+      </c>
+      <c r="R49" t="n">
+        <v>6987069</v>
+      </c>
+      <c r="S49" t="n">
+        <v>25</v>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Oviken</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>2024-11-17</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>2024-11-17</t>
+        </is>
+      </c>
+      <c r="AD49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT49" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>Klas Andersson</t>
+        </is>
+      </c>
+      <c r="AX49" t="inlineStr">
+        <is>
+          <t>Klas Andersson</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>121227124</v>
+      </c>
+      <c r="B50" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>Strömborgsmyren, Jmt</t>
+        </is>
+      </c>
+      <c r="Q50" t="n">
+        <v>459222</v>
+      </c>
+      <c r="R50" t="n">
+        <v>6987047</v>
+      </c>
+      <c r="S50" t="n">
+        <v>25</v>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Oviken</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>2024-11-17</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>2024-11-17</t>
+        </is>
+      </c>
+      <c r="AD50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT50" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>Klas Andersson</t>
+        </is>
+      </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>Klas Andersson</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>121227125</v>
+      </c>
+      <c r="B51" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>Strömborgsmyren, Jmt</t>
+        </is>
+      </c>
+      <c r="Q51" t="n">
+        <v>459256</v>
+      </c>
+      <c r="R51" t="n">
+        <v>6987066</v>
+      </c>
+      <c r="S51" t="n">
+        <v>25</v>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>Oviken</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>2024-11-17</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>2024-11-17</t>
+        </is>
+      </c>
+      <c r="AD51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT51" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>Klas Andersson</t>
+        </is>
+      </c>
+      <c r="AX51" t="inlineStr">
+        <is>
+          <t>Klas Andersson</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>121227129</v>
+      </c>
+      <c r="B52" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>Strömborgsmyren, Jmt</t>
+        </is>
+      </c>
+      <c r="Q52" t="n">
+        <v>459255</v>
+      </c>
+      <c r="R52" t="n">
+        <v>6987069</v>
+      </c>
+      <c r="S52" t="n">
+        <v>25</v>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>Oviken</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>2024-11-17</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>2024-11-17</t>
+        </is>
+      </c>
+      <c r="AD52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT52" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>Klas Andersson</t>
+        </is>
+      </c>
+      <c r="AX52" t="inlineStr">
+        <is>
+          <t>Klas Andersson</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>121210312</v>
+      </c>
+      <c r="B53" t="n">
+        <v>83290</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>6439</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Gulnål</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Chaenotheca brachypoda</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>(Ach.) Tibell</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>Strömborgsmyren, Jmt</t>
+        </is>
+      </c>
+      <c r="Q53" t="n">
+        <v>459362</v>
+      </c>
+      <c r="R53" t="n">
+        <v>6987057</v>
+      </c>
+      <c r="S53" t="n">
+        <v>20</v>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>Oviken</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>2024-11-16</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>2024-11-16</t>
+        </is>
+      </c>
+      <c r="AD53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT53" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>Klas Andersson</t>
+        </is>
+      </c>
+      <c r="AX53" t="inlineStr">
+        <is>
+          <t>Klas Andersson</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>121227088</v>
+      </c>
+      <c r="B54" t="n">
+        <v>83290</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>6439</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Gulnål</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Chaenotheca brachypoda</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>(Ach.) Tibell</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>Strömborgsmyren, Jmt</t>
+        </is>
+      </c>
+      <c r="Q54" t="n">
+        <v>459493</v>
+      </c>
+      <c r="R54" t="n">
+        <v>6987097</v>
+      </c>
+      <c r="S54" t="n">
+        <v>25</v>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>Oviken</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>2024-11-17</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>2024-11-17</t>
+        </is>
+      </c>
+      <c r="AD54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT54" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>Klas Andersson</t>
+        </is>
+      </c>
+      <c r="AX54" t="inlineStr">
+        <is>
+          <t>Klas Andersson</t>
+        </is>
+      </c>
+      <c r="AY54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>121210334</v>
+      </c>
+      <c r="B55" t="n">
+        <v>83307</v>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>6440</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Vitgrynig nållav</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Chaenotheca subroscida</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>Strömborgsmyren, Jmt</t>
+        </is>
+      </c>
+      <c r="Q55" t="n">
+        <v>459371</v>
+      </c>
+      <c r="R55" t="n">
+        <v>6987042</v>
+      </c>
+      <c r="S55" t="n">
+        <v>20</v>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>Oviken</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>2024-11-16</t>
+        </is>
+      </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>2024-11-16</t>
+        </is>
+      </c>
+      <c r="AD55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT55" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>Klas Andersson</t>
+        </is>
+      </c>
+      <c r="AX55" t="inlineStr">
+        <is>
+          <t>Klas Andersson</t>
+        </is>
+      </c>
+      <c r="AY55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>121210317</v>
+      </c>
+      <c r="B56" t="n">
+        <v>80468</v>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>6464</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Luddlav</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Nephroma resupinatum</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>Strömborgsmyren, Jmt</t>
+        </is>
+      </c>
+      <c r="Q56" t="n">
+        <v>459209</v>
+      </c>
+      <c r="R56" t="n">
+        <v>6986978</v>
+      </c>
+      <c r="S56" t="n">
+        <v>20</v>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>Oviken</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr">
+        <is>
+          <t>2024-11-16</t>
+        </is>
+      </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>2024-11-16</t>
+        </is>
+      </c>
+      <c r="AD56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT56" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>Klas Andersson</t>
+        </is>
+      </c>
+      <c r="AX56" t="inlineStr">
+        <is>
+          <t>Klas Andersson</t>
+        </is>
+      </c>
+      <c r="AY56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>121210315</v>
+      </c>
+      <c r="B57" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
+      <c r="K57" t="inlineStr"/>
+      <c r="L57" t="inlineStr"/>
+      <c r="M57" t="inlineStr"/>
+      <c r="N57" t="inlineStr"/>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>Strömborgsmyren, Jmt</t>
+        </is>
+      </c>
+      <c r="Q57" t="n">
+        <v>459269</v>
+      </c>
+      <c r="R57" t="n">
+        <v>6987021</v>
+      </c>
+      <c r="S57" t="n">
+        <v>20</v>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>Oviken</t>
+        </is>
+      </c>
+      <c r="Y57" t="inlineStr">
+        <is>
+          <t>2024-11-16</t>
+        </is>
+      </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>2024-11-16</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>Rel. färska ringhack på gran, hördes också varnande</t>
+        </is>
+      </c>
+      <c r="AD57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT57" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>Klas Andersson</t>
+        </is>
+      </c>
+      <c r="AX57" t="inlineStr">
+        <is>
+          <t>Klas Andersson</t>
+        </is>
+      </c>
+      <c r="AY57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>121227135</v>
+      </c>
+      <c r="B58" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
+      <c r="K58" t="inlineStr"/>
+      <c r="L58" t="inlineStr"/>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N58" t="inlineStr"/>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>Strömborgsmyren, Jmt</t>
+        </is>
+      </c>
+      <c r="Q58" t="n">
+        <v>459252</v>
+      </c>
+      <c r="R58" t="n">
+        <v>6987032</v>
+      </c>
+      <c r="S58" t="n">
+        <v>25</v>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>Oviken</t>
+        </is>
+      </c>
+      <c r="Y58" t="inlineStr">
+        <is>
+          <t>2024-11-17</t>
+        </is>
+      </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>2024-11-17</t>
+        </is>
+      </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
+      <c r="AD58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT58" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>Klas Andersson</t>
+        </is>
+      </c>
+      <c r="AX58" t="inlineStr">
+        <is>
+          <t>Klas Andersson</t>
+        </is>
+      </c>
+      <c r="AY58" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>128970369</v>
+      </c>
+      <c r="B59" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr"/>
+      <c r="L59" t="inlineStr"/>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N59" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>Strömborgen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q59" t="n">
+        <v>459223</v>
+      </c>
+      <c r="R59" t="n">
+        <v>6987032</v>
+      </c>
+      <c r="S59" t="n">
+        <v>10</v>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>Oviken</t>
+        </is>
+      </c>
+      <c r="Y59" t="inlineStr">
+        <is>
+          <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>Sågs födosökande lågt ner på stammen av granar.</t>
+        </is>
+      </c>
+      <c r="AD59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT59" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
           <t>Benny Öwre</t>
         </is>
       </c>
-      <c r="AX45" t="inlineStr">
+      <c r="AX59" t="inlineStr">
         <is>
           <t>Benny Öwre</t>
         </is>
       </c>
-      <c r="AY45" t="inlineStr"/>
+      <c r="AY59" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>128970371</v>
+      </c>
+      <c r="B60" t="n">
+        <v>58057</v>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>103031</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Lavskrika</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Perisoreus infaustus</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr"/>
+      <c r="L60" t="inlineStr"/>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N60" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>Strömborgen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q60" t="n">
+        <v>459308</v>
+      </c>
+      <c r="R60" t="n">
+        <v>6987027</v>
+      </c>
+      <c r="S60" t="n">
+        <v>10</v>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W60" t="inlineStr">
+        <is>
+          <t>Oviken</t>
+        </is>
+      </c>
+      <c r="Y60" t="inlineStr">
+        <is>
+          <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="AD60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT60" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX60" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY60" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>121125621</v>
+      </c>
+      <c r="B61" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>Stenmyrflon, Stenmyrflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q61" t="n">
+        <v>459423</v>
+      </c>
+      <c r="R61" t="n">
+        <v>6986917</v>
+      </c>
+      <c r="S61" t="n">
+        <v>20</v>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W61" t="inlineStr">
+        <is>
+          <t>Oviken</t>
+        </is>
+      </c>
+      <c r="Y61" t="inlineStr">
+        <is>
+          <t>2024-11-11</t>
+        </is>
+      </c>
+      <c r="Z61" t="inlineStr">
+        <is>
+          <t>09:51</t>
+        </is>
+      </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>2024-11-11</t>
+        </is>
+      </c>
+      <c r="AB61" t="inlineStr">
+        <is>
+          <t>09:51</t>
+        </is>
+      </c>
+      <c r="AD61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT61" t="inlineStr"/>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>Jenny Persson</t>
+        </is>
+      </c>
+      <c r="AX61" t="inlineStr">
+        <is>
+          <t>Jenny Persson</t>
+        </is>
+      </c>
+      <c r="AY61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>121125895</v>
+      </c>
+      <c r="B62" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>Stenmyrflon, Stenmyrflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q62" t="n">
+        <v>459413</v>
+      </c>
+      <c r="R62" t="n">
+        <v>6986953</v>
+      </c>
+      <c r="S62" t="n">
+        <v>15</v>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W62" t="inlineStr">
+        <is>
+          <t>Oviken</t>
+        </is>
+      </c>
+      <c r="Y62" t="inlineStr">
+        <is>
+          <t>2024-11-11</t>
+        </is>
+      </c>
+      <c r="Z62" t="inlineStr">
+        <is>
+          <t>10:08</t>
+        </is>
+      </c>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>2024-11-11</t>
+        </is>
+      </c>
+      <c r="AB62" t="inlineStr">
+        <is>
+          <t>10:08</t>
+        </is>
+      </c>
+      <c r="AD62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT62" t="inlineStr"/>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>Jenny Persson</t>
+        </is>
+      </c>
+      <c r="AX62" t="inlineStr">
+        <is>
+          <t>Jenny Persson</t>
+        </is>
+      </c>
+      <c r="AY62" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>121126591</v>
+      </c>
+      <c r="B63" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>Strömborgsmyren, Strömborgsmyren, Jmt</t>
+        </is>
+      </c>
+      <c r="Q63" t="n">
+        <v>459352</v>
+      </c>
+      <c r="R63" t="n">
+        <v>6987044</v>
+      </c>
+      <c r="S63" t="n">
+        <v>20</v>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W63" t="inlineStr">
+        <is>
+          <t>Oviken</t>
+        </is>
+      </c>
+      <c r="Y63" t="inlineStr">
+        <is>
+          <t>2024-11-11</t>
+        </is>
+      </c>
+      <c r="Z63" t="inlineStr">
+        <is>
+          <t>11:03</t>
+        </is>
+      </c>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>2024-11-11</t>
+        </is>
+      </c>
+      <c r="AB63" t="inlineStr">
+        <is>
+          <t>11:03</t>
+        </is>
+      </c>
+      <c r="AD63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT63" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>Jenny Persson</t>
+        </is>
+      </c>
+      <c r="AX63" t="inlineStr">
+        <is>
+          <t>Jenny Persson</t>
+        </is>
+      </c>
+      <c r="AY63" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>121131481</v>
+      </c>
+      <c r="B64" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>Stenmyrflon, Stenmyrflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q64" t="n">
+        <v>459308</v>
+      </c>
+      <c r="R64" t="n">
+        <v>6987012</v>
+      </c>
+      <c r="S64" t="n">
+        <v>15</v>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W64" t="inlineStr">
+        <is>
+          <t>Oviken</t>
+        </is>
+      </c>
+      <c r="Y64" t="inlineStr">
+        <is>
+          <t>2024-11-11</t>
+        </is>
+      </c>
+      <c r="Z64" t="inlineStr">
+        <is>
+          <t>14:41</t>
+        </is>
+      </c>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>2024-11-11</t>
+        </is>
+      </c>
+      <c r="AB64" t="inlineStr">
+        <is>
+          <t>14:41</t>
+        </is>
+      </c>
+      <c r="AD64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT64" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>Jenny Persson</t>
+        </is>
+      </c>
+      <c r="AX64" t="inlineStr">
+        <is>
+          <t>Jenny Persson</t>
+        </is>
+      </c>
+      <c r="AY64" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>121210325</v>
+      </c>
+      <c r="B65" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr"/>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>Strömborgsmyren, Jmt</t>
+        </is>
+      </c>
+      <c r="Q65" t="n">
+        <v>459361</v>
+      </c>
+      <c r="R65" t="n">
+        <v>6986971</v>
+      </c>
+      <c r="S65" t="n">
+        <v>20</v>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W65" t="inlineStr">
+        <is>
+          <t>Oviken</t>
+        </is>
+      </c>
+      <c r="Y65" t="inlineStr">
+        <is>
+          <t>2024-11-16</t>
+        </is>
+      </c>
+      <c r="AA65" t="inlineStr">
+        <is>
+          <t>2024-11-16</t>
+        </is>
+      </c>
+      <c r="AD65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT65" t="inlineStr"/>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>Klas Andersson</t>
+        </is>
+      </c>
+      <c r="AX65" t="inlineStr">
+        <is>
+          <t>Klas Andersson</t>
+        </is>
+      </c>
+      <c r="AY65" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 39282-2025 artfynd.xlsx
+++ b/artfynd/A 39282-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY65"/>
+  <dimension ref="A1:AZ65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121210313</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -875,6 +885,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121210330</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -972,6 +987,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121210331</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1069,6 +1089,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121227110</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1166,6 +1191,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121227111</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1272,6 +1302,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121227113</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1369,6 +1404,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121210318</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1466,6 +1506,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121227089</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1563,6 +1608,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121210316</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1670,6 +1720,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120971712</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1777,6 +1832,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121125668</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1874,6 +1934,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121210350</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1971,6 +2036,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121210351</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2068,6 +2138,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121227101</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2165,6 +2240,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121227102</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2262,6 +2342,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121227103</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2359,6 +2444,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121210321</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2456,6 +2546,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121227105</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2553,6 +2648,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121227106</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2650,6 +2750,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121227109</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2747,6 +2852,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121227086</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2854,6 +2964,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120971669</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2961,6 +3076,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120972218</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3068,6 +3188,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120972337</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3175,6 +3300,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121125770</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3282,6 +3412,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121125947</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3379,6 +3514,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121210354</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3476,6 +3616,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121210355</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3573,6 +3718,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121210356</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3670,6 +3820,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121210358</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3767,6 +3922,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121227114</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3864,6 +4024,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121227115</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -3961,6 +4126,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121227116</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4058,6 +4228,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121227117</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4155,6 +4330,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121227118</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4252,6 +4432,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121227119</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4349,6 +4534,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121227120</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4446,6 +4636,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121227121</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4543,6 +4738,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121227122</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4640,6 +4840,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121227123</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4737,6 +4942,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121227124</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -4834,6 +5044,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121227125</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -4931,6 +5146,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121227129</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5028,6 +5248,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121210312</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5125,6 +5350,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121227088</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5222,6 +5452,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121210334</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5319,6 +5554,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121227095</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5416,6 +5656,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121227096</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5513,6 +5758,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121227097</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -5610,6 +5860,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121227094</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -5707,6 +5962,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121210317</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -5813,6 +6073,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121210315</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -5931,6 +6196,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121227134</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6041,6 +6311,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121227135</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6159,6 +6434,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128970369</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6261,6 +6541,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129593946</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6363,6 +6648,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129593950</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -6460,6 +6750,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121210319</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -6573,6 +6868,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128970371</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -6689,6 +6989,11 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121125621</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -6805,6 +7110,11 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121125895</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -6921,6 +7231,11 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121126591</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -7037,6 +7352,11 @@
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121131481</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -7134,8 +7454,79 @@
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121210325</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>